--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484324_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484324_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9279</v>
+        <v>2.6366</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7019</v>
+        <v>2.5196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.226</v>
+        <v>0.117</v>
       </c>
       <c r="G2" t="n">
         <v>1.4529</v>
@@ -610,13 +610,13 @@
         <v>2.3441</v>
       </c>
       <c r="S2" t="n">
-        <v>0.662</v>
+        <v>0.3708</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5752</v>
+        <v>0.3929</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0868</v>
+        <v>-0.0221</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5545</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7962</v>
+        <v>1.8299</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1168</v>
+        <v>1.3684</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6795</v>
+        <v>0.4616</v>
       </c>
       <c r="G3" t="n">
         <v>-1.1178</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8825</v>
+        <v>0.9162</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5986</v>
+        <v>0.8502</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2838</v>
+        <v>0.0659</v>
       </c>
       <c r="V3" t="n">
         <v>0.6642</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0111</v>
+        <v>1.4645</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5134</v>
+        <v>1.7762</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5023</v>
+        <v>-0.3117</v>
       </c>
       <c r="G4" t="n">
         <v>-1.3488</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.148</v>
+        <v>0.3054</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0989</v>
+        <v>0.1638</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.049</v>
+        <v>0.1416</v>
       </c>
       <c r="V4" t="n">
         <v>0.5545</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0988</v>
+        <v>1.3763</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6491</v>
+        <v>2.5253</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7478</v>
+        <v>-1.1491</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3751</v>
+        <v>-1.4462</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1998</v>
+        <v>-1.0954</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1753</v>
+        <v>-0.3508</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0405</v>
+        <v>1.5599</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.9657</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0405</v>
+        <v>0.5942</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3346</v>
+        <v>-3.0061</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1998</v>
+        <v>-2.0611</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1348</v>
+        <v>-0.9449</v>
       </c>
       <c r="P5" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R5" t="n">
-        <v>0.586</v>
+        <v>1.9534</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4754</v>
+        <v>0.108</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3026</v>
+        <v>0.2044</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1728</v>
+        <v>-0.0964</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3869</v>
+        <v>2.7145</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3869</v>
+        <v>2.7145</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1838</v>
+        <v>0.3555</v>
       </c>
       <c r="E6" t="n">
-        <v>1.292</v>
+        <v>-0.4469</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.4759</v>
+        <v>0.8023</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4462</v>
+        <v>0.3751</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0954</v>
+        <v>0.1998</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3508</v>
+        <v>0.1753</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5599</v>
+        <v>0.0405</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9657</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5942</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.0061</v>
+        <v>0.3346</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.0611</v>
+        <v>0.1998</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9449</v>
+        <v>0.1348</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9534</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.4521</v>
+        <v>-0.2187</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0289</v>
+        <v>-0.1004</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4232</v>
+        <v>-0.1183</v>
       </c>
       <c r="V6" t="n">
-        <v>2.7145</v>
+        <v>-0.3869</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7145</v>
+        <v>-0.3869</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.053</v>
+        <v>-0.8097</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6747</v>
+        <v>-0.513</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3783</v>
+        <v>-0.2966</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4747</v>
@@ -1000,13 +1000,13 @@
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1876</v>
+        <v>0.0557</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1073</v>
+        <v>0.0544</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0803</v>
+        <v>0.0014</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5319</v>
+        <v>-1.658</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.9417</v>
+        <v>-2.2857</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4098</v>
+        <v>0.6277</v>
       </c>
       <c r="G8" t="n">
         <v>0.254</v>
@@ -1078,13 +1078,13 @@
         <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8002</v>
+        <v>0.6741</v>
       </c>
       <c r="T8" t="n">
-        <v>0.864</v>
+        <v>0.5201</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0639</v>
+        <v>0.154</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2186</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1433</v>
+        <v>-3.2772</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8807</v>
+        <v>-1.1235</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2626</v>
+        <v>-2.1537</v>
       </c>
       <c r="G9" t="n">
         <v>-3.4526</v>
@@ -1156,13 +1156,13 @@
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2767</v>
+        <v>-0.4106</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3247</v>
+        <v>0.0819</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.6015</v>
+        <v>-0.4925</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5831</v>
+        <v>-3.5013</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2779</v>
+        <v>-2.9222</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3052</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5108</v>
+        <v>-2.725</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.7552</v>
+        <v>0.6465</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7556</v>
+        <v>-3.3715</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6299</v>
+        <v>-1.5708</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5756</v>
+        <v>0.4515</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0543</v>
+        <v>-2.0223</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1407</v>
+        <v>-1.1542</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.3308</v>
+        <v>0.1949</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8099</v>
+        <v>-1.3492</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5395</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S10" t="n">
-        <v>1.522</v>
+        <v>0.3604</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0539</v>
+        <v>0.3247</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4681</v>
+        <v>0.0357</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.0549</v>
+        <v>-0.9414</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0549</v>
+        <v>0.2772</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.405</v>
+        <v>-4.6855</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4502</v>
+        <v>-3.0263</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9548</v>
+        <v>-1.6592</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.6156</v>
+        <v>-2.5108</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4032</v>
+        <v>-1.7552</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2124</v>
+        <v>-0.7556</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.5909</v>
+        <v>0.6299</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.9977</v>
+        <v>0.5756</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5931999999999999</v>
+        <v>0.0543</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.0247</v>
+        <v>-3.1407</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.4055</v>
+        <v>-2.3308</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.6192</v>
+        <v>-0.8099</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.1488</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.9069</v>
       </c>
       <c r="R11" t="n">
-        <v>1.7581</v>
+        <v>1.3674</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6449</v>
+        <v>0.4196</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3331</v>
+        <v>0.3055</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3118</v>
+        <v>0.1141</v>
       </c>
       <c r="V11" t="n">
-        <v>2.7145</v>
+        <v>-0.0549</v>
       </c>
       <c r="W11" t="n">
-        <v>2.7145</v>
+        <v>-0.0549</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.5947</v>
+        <v>-4.8208</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.8522</v>
+        <v>-2.4303</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7425</v>
+        <v>-2.3906</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.725</v>
+        <v>-5.6156</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6465</v>
+        <v>-3.4032</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.3715</v>
+        <v>-2.2124</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5708</v>
+        <v>-1.5909</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4515</v>
+        <v>-0.9977</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0223</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1542</v>
+        <v>-4.0247</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1949</v>
+        <v>-2.4055</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.3492</v>
+        <v>-1.6192</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.1953</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9534</v>
+        <v>-3.9069</v>
       </c>
       <c r="R12" t="n">
         <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.733</v>
+        <v>0.229</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6052</v>
+        <v>0.353</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1277</v>
+        <v>-0.124</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9414</v>
+        <v>2.7145</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2772</v>
+        <v>2.7145</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.8254</v>
+        <v>-5.4888</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.5645</v>
+        <v>-2.2006</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2609</v>
+        <v>-3.2882</v>
       </c>
       <c r="G13" t="n">
         <v>-5.3643</v>
@@ -1468,13 +1468,13 @@
         <v>0.7814</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.07870000000000001</v>
+        <v>0.258</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0083</v>
+        <v>0.3722</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.1143</v>
       </c>
       <c r="V13" t="n">
         <v>-1.1638</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-17.4862</v>
+        <v>-16.5785</v>
       </c>
       <c r="E14" t="n">
-        <v>-7.666899999999999</v>
+        <v>-6.759</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.8194</v>
+        <v>-9.819600000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-21.9738</v>
@@ -1516,7 +1516,7 @@
         <v>-12.5315</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.442399999999999</v>
+        <v>-9.442400000000001</v>
       </c>
       <c r="J14" t="n">
         <v>-1.824</v>
@@ -1546,13 +1546,13 @@
         <v>16.604</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1601</v>
+        <v>3.0679</v>
       </c>
       <c r="T14" t="n">
-        <v>2.6149</v>
+        <v>3.5227</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4549</v>
+        <v>-0.4549000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>2.3276</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.2839</v>
+        <v>9.905799999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>9.599299999999999</v>
+        <v>8.385999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.6846</v>
+        <v>1.5198</v>
       </c>
       <c r="G15" t="n">
         <v>9.340999999999999</v>
@@ -1624,13 +1624,13 @@
         <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>2.3727</v>
+        <v>0.9946</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8491</v>
+        <v>0.6357</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5236</v>
+        <v>0.3589</v>
       </c>
       <c r="V15" t="n">
         <v>-1.9925</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.3393</v>
+        <v>5.8411</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0277</v>
+        <v>3.23</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3115</v>
+        <v>2.6111</v>
       </c>
       <c r="G16" t="n">
         <v>2.8737</v>
@@ -1702,13 +1702,13 @@
         <v>2.5395</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7027</v>
+        <v>-0.2009</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0221</v>
+        <v>0.2244</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7248</v>
+        <v>-0.4252</v>
       </c>
       <c r="V16" t="n">
         <v>1.6056</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9229</v>
+        <v>4.0771</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5623</v>
+        <v>2.8962</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3605</v>
+        <v>1.1809</v>
       </c>
       <c r="G17" t="n">
-        <v>3.7851</v>
+        <v>3.0711</v>
       </c>
       <c r="H17" t="n">
-        <v>3.7583</v>
+        <v>0.1842</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0268</v>
+        <v>2.8869</v>
       </c>
       <c r="J17" t="n">
-        <v>3.0011</v>
+        <v>3.3057</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3781</v>
+        <v>0.1483</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.377</v>
+        <v>3.1573</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7841</v>
+        <v>-0.2346</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3802</v>
+        <v>0.0359</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4039</v>
+        <v>-0.2704</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R17" t="n">
         <v>2.7348</v>
       </c>
       <c r="S17" t="n">
-        <v>0.575</v>
+        <v>-0.6266</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5147</v>
+        <v>0.0834</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0603</v>
+        <v>-0.71</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.2186</v>
+        <v>1.8279</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2031</v>
+        <v>3.9215</v>
       </c>
       <c r="E18" t="n">
-        <v>2.5928</v>
+        <v>1.5623</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6103</v>
+        <v>2.3592</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0711</v>
+        <v>3.7851</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1842</v>
+        <v>3.7583</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8869</v>
+        <v>0.0268</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3057</v>
+        <v>3.0011</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1483</v>
+        <v>3.3781</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1573</v>
+        <v>-0.377</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2346</v>
+        <v>0.7841</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0359</v>
+        <v>0.3802</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2704</v>
+        <v>0.4039</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
         <v>2.7348</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.5005</v>
+        <v>0.5736</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.22</v>
+        <v>0.5147</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2806</v>
+        <v>0.059</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8279</v>
+        <v>-1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4373</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6741</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.5805</v>
+        <v>0.4794</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0936</v>
+        <v>0.2026</v>
       </c>
       <c r="G19" t="n">
         <v>3.4313</v>
@@ -1936,13 +1936,13 @@
         <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6482</v>
+        <v>-0.6404</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0384</v>
+        <v>-0.1395</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6098</v>
+        <v>-0.5009</v>
       </c>
       <c r="V19" t="n">
         <v>-1.7182</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2796</v>
+        <v>0.618</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4592</v>
+        <v>-1.257</v>
       </c>
       <c r="F20" t="n">
-        <v>1.7388</v>
+        <v>1.875</v>
       </c>
       <c r="G20" t="n">
         <v>0.6614</v>
@@ -2014,13 +2014,13 @@
         <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6906</v>
+        <v>-0.3522</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5447</v>
+        <v>-0.3425</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1459</v>
+        <v>-0.0097</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2772</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0906</v>
+        <v>-1.1025</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.648</v>
+        <v>-1.1424</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5573</v>
+        <v>0.0398</v>
       </c>
       <c r="G21" t="n">
         <v>0.7374000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>0.5078</v>
+        <v>0.4959</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3494</v>
+        <v>0.1562</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8571</v>
+        <v>0.3397</v>
       </c>
       <c r="V21" t="n">
         <v>-1.1638</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.6253</v>
+        <v>-1.3622</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6962</v>
+        <v>0.7973</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3215</v>
+        <v>-2.1595</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2212</v>
@@ -2170,13 +2170,13 @@
         <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1539</v>
+        <v>-0.8907</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4842</v>
+        <v>-0.3831</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6697</v>
+        <v>-0.5077</v>
       </c>
       <c r="V22" t="n">
         <v>0.5545</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1065</v>
+        <v>-1.9989</v>
       </c>
       <c r="E23" t="n">
         <v>-3.1637</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0572</v>
+        <v>1.1648</v>
       </c>
       <c r="G23" t="n">
         <v>-1.0392</v>
@@ -2248,13 +2248,13 @@
         <v>0.7814</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2273</v>
+        <v>-0.1197</v>
       </c>
       <c r="T23" t="n">
         <v>0.0689</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2961</v>
+        <v>-0.1886</v>
       </c>
       <c r="V23" t="n">
         <v>0.3321</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.3942</v>
+        <v>-2.4215</v>
       </c>
       <c r="E24" t="n">
         <v>-1.9686</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4256</v>
+        <v>-0.4528</v>
       </c>
       <c r="G24" t="n">
         <v>0.3334</v>
@@ -2326,13 +2326,13 @@
         <v>0.1953</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6923</v>
+        <v>-0.7195</v>
       </c>
       <c r="T24" t="n">
         <v>-0.3631</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3291</v>
+        <v>-0.3564</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2772</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>17.48629999999999</v>
+        <v>18.1604</v>
       </c>
       <c r="E25" t="n">
-        <v>9.819299999999998</v>
+        <v>9.8195</v>
       </c>
       <c r="F25" t="n">
-        <v>7.666700000000001</v>
+        <v>8.3409</v>
       </c>
       <c r="G25" t="n">
         <v>21.974</v>
@@ -2404,13 +2404,13 @@
         <v>16.6041</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.16</v>
+        <v>-1.4859</v>
       </c>
       <c r="T25" t="n">
-        <v>0.4550000000000001</v>
+        <v>0.4551000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.615</v>
+        <v>-1.9409</v>
       </c>
       <c r="V25" t="n">
         <v>-2.3274</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484324_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484324_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,31 +570,31 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6366</v>
+        <v>2.0296</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5196</v>
+        <v>1.9126</v>
       </c>
       <c r="F2" t="n">
         <v>0.117</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4529</v>
+        <v>0.8459</v>
       </c>
       <c r="H2" t="n">
         <v>1.3988</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0541</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8262</v>
+        <v>2.2192</v>
       </c>
       <c r="K2" t="n">
         <v>2.232</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5942</v>
+        <v>-0.0128</v>
       </c>
       <c r="M2" t="n">
         <v>-1.3733</v>
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.8317</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.8317</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3555</v>
+        <v>0.607</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4469</v>
+        <v>0.607</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8023</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3751</v>
+        <v>0.607</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1998</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1753</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3346</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1998</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2187</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1004</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1183</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SELLARÈS GIRALT</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8097</v>
+        <v>0.3555</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.513</v>
+        <v>-0.4469</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2966</v>
+        <v>0.8023</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4747</v>
+        <v>0.3751</v>
       </c>
       <c r="H7" t="n">
         <v>0.1998</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6745</v>
+        <v>0.1753</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4093</v>
+        <v>0.0405</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4093</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.884</v>
+        <v>0.3346</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2095</v>
+        <v>0.1998</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6745</v>
+        <v>0.1348</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0557</v>
+        <v>-0.2187</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0544</v>
+        <v>-0.1004</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0014</v>
+        <v>-0.1183</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>M. SELLARÈS GIRALT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.658</v>
+        <v>0.307</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2857</v>
+        <v>0.307</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6277</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.254</v>
+        <v>0.307</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1734</v>
+        <v>0.307</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0805</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1244</v>
+        <v>0.307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0435</v>
+        <v>0.307</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1296</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0004</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.3674</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6741</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5201</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.154</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>M. SELLARES GIRALT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2772</v>
+        <v>-1.1166</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1235</v>
+        <v>-0.82</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1537</v>
+        <v>-0.2966</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.4526</v>
+        <v>-0.7817</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.2789</v>
+        <v>-0.1072</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1737</v>
+        <v>-0.6745</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2054</v>
+        <v>0.1023</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2459</v>
+        <v>0.1023</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.2472</v>
+        <v>-0.884</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.033</v>
+        <v>-0.2095</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2142</v>
+        <v>-0.6745</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
         <v>0.586</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4106</v>
+        <v>0.0557</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0819</v>
+        <v>0.0544</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.4925</v>
+        <v>0.0014</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,12 +1212,17 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5013</v>
+        <v>-1.658</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9222</v>
+        <v>-2.2857</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.6277</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.725</v>
+        <v>0.254</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6465</v>
+        <v>0.1734</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.3715</v>
+        <v>0.0805</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.5708</v>
+        <v>0.1244</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4515</v>
+        <v>0.0435</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0223</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1542</v>
+        <v>0.1296</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1949</v>
+        <v>0.13</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3492</v>
+        <v>-0.0004</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1953</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3604</v>
+        <v>0.6741</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3247</v>
+        <v>0.5201</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0357</v>
+        <v>0.154</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9414</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.6855</v>
+        <v>-3.2772</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.0263</v>
+        <v>-1.1235</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6592</v>
+        <v>-2.1537</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5108</v>
+        <v>-3.4526</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.7552</v>
+        <v>-2.2789</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7556</v>
+        <v>-1.1737</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6299</v>
+        <v>-1.2054</v>
       </c>
       <c r="K11" t="n">
-        <v>0.5756</v>
+        <v>-1.2459</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0543</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.1407</v>
+        <v>-2.2472</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.3308</v>
+        <v>-1.033</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8099</v>
+        <v>-1.2142</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.5395</v>
+        <v>0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4196</v>
+        <v>-0.4106</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3055</v>
+        <v>0.0819</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1141</v>
+        <v>-0.4925</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8208</v>
+        <v>-3.5013</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4303</v>
+        <v>-2.9222</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3906</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.6156</v>
+        <v>-2.725</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.4032</v>
+        <v>0.6465</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2124</v>
+        <v>-3.3715</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5909</v>
+        <v>-1.5708</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9977</v>
+        <v>0.4515</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-2.0223</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.0247</v>
+        <v>-1.1542</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.4055</v>
+        <v>0.1949</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.6192</v>
+        <v>-1.3492</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1488</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.9069</v>
+        <v>-1.9534</v>
       </c>
       <c r="R12" t="n">
         <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>0.229</v>
+        <v>0.3604</v>
       </c>
       <c r="T12" t="n">
-        <v>0.353</v>
+        <v>0.3247</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.124</v>
+        <v>0.0357</v>
       </c>
       <c r="V12" t="n">
-        <v>2.7145</v>
+        <v>-0.9414</v>
       </c>
       <c r="W12" t="n">
-        <v>2.7145</v>
+        <v>0.2772</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1483,78 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.4888</v>
+        <v>-4.6855</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.2006</v>
+        <v>-3.0263</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.2882</v>
+        <v>-1.6592</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.3643</v>
+        <v>-2.5108</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.8422</v>
+        <v>-1.7552</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.5221</v>
+        <v>-0.7556</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.5728</v>
+        <v>0.6299</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.2651</v>
+        <v>0.5756</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.3077</v>
+        <v>0.0543</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.7915</v>
+        <v>-3.1407</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.5771</v>
+        <v>-2.3308</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.2144</v>
+        <v>-0.8099</v>
       </c>
       <c r="P13" t="n">
-        <v>0.7814</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R13" t="n">
-        <v>0.7814</v>
+        <v>1.3674</v>
       </c>
       <c r="S13" t="n">
-        <v>0.258</v>
+        <v>0.4196</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3722</v>
+        <v>0.3055</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1143</v>
+        <v>0.1141</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1638</v>
+        <v>-0.0549</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,229 +1566,240 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-16.5785</v>
+        <v>-4.8208</v>
       </c>
       <c r="E14" t="n">
-        <v>-6.759</v>
+        <v>-2.4303</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.819600000000001</v>
+        <v>-2.3906</v>
       </c>
       <c r="G14" t="n">
-        <v>-21.9738</v>
+        <v>-5.6156</v>
       </c>
       <c r="H14" t="n">
-        <v>-12.5315</v>
+        <v>-3.4032</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.442400000000001</v>
+        <v>-2.2124</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.824</v>
+        <v>-1.5909</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.153999999999999</v>
+        <v>-0.9977</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6699999999999999</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-20.1498</v>
+        <v>-4.0247</v>
       </c>
       <c r="N14" t="n">
-        <v>-11.3775</v>
+        <v>-2.4055</v>
       </c>
       <c r="O14" t="n">
-        <v>-8.7723</v>
+        <v>-1.6192</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.999999999987796e-05</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q14" t="n">
-        <v>-16.6041</v>
+        <v>-3.9069</v>
       </c>
       <c r="R14" t="n">
-        <v>16.604</v>
+        <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0679</v>
+        <v>0.229</v>
       </c>
       <c r="T14" t="n">
-        <v>3.5227</v>
+        <v>0.353</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4549000000000001</v>
+        <v>-0.124</v>
       </c>
       <c r="V14" t="n">
-        <v>2.3276</v>
+        <v>2.7145</v>
       </c>
       <c r="W14" t="n">
-        <v>8.1464</v>
+        <v>2.7145</v>
       </c>
       <c r="X14" t="n">
-        <v>-5.8189</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.905799999999999</v>
+        <v>-5.4888</v>
       </c>
       <c r="E15" t="n">
-        <v>8.385999999999999</v>
+        <v>-2.2006</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5198</v>
+        <v>-3.2882</v>
       </c>
       <c r="G15" t="n">
-        <v>9.340999999999999</v>
+        <v>-5.3643</v>
       </c>
       <c r="H15" t="n">
-        <v>5.3753</v>
+        <v>-2.8422</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9656</v>
+        <v>-2.5221</v>
       </c>
       <c r="J15" t="n">
-        <v>8.891500000000001</v>
+        <v>-2.5728</v>
       </c>
       <c r="K15" t="n">
-        <v>5.0601</v>
+        <v>-1.2651</v>
       </c>
       <c r="L15" t="n">
-        <v>3.8314</v>
+        <v>-1.3077</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4494</v>
+        <v>-2.7915</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3152</v>
+        <v>-1.5771</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1342</v>
+        <v>-1.2144</v>
       </c>
       <c r="P15" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.5395</v>
+        <v>0.7814</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9946</v>
+        <v>0.258</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6357</v>
+        <v>0.3722</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3589</v>
+        <v>-0.1143</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.9925</v>
+        <v>-1.1638</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.1646</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.8279</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. DI BONAVENTURA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>TENEA-C.B. ESPARREGUERA</t>
         </is>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.8411</v>
+        <v>-16.5784</v>
       </c>
       <c r="E16" t="n">
-        <v>3.23</v>
+        <v>-6.759</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6111</v>
+        <v>-9.819599999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8737</v>
+        <v>-21.9738</v>
       </c>
       <c r="H16" t="n">
-        <v>1.6455</v>
+        <v>-12.5315</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2282</v>
+        <v>-9.442400000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>2.7637</v>
+        <v>-1.824000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.5349</v>
+        <v>-1.153999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2288</v>
+        <v>-0.6699999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>0.11</v>
+        <v>-20.1498</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1105</v>
+        <v>-11.3775</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-8.7723</v>
       </c>
       <c r="P16" t="n">
-        <v>1.5627</v>
+        <v>-9.999999999987796e-05</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9767</v>
+        <v>-16.6041</v>
       </c>
       <c r="R16" t="n">
-        <v>2.5395</v>
+        <v>16.604</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2009</v>
+        <v>3.0679</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2244</v>
+        <v>3.5227</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4252</v>
+        <v>-0.4549</v>
       </c>
       <c r="V16" t="n">
-        <v>1.6056</v>
+        <v>2.3276</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2186</v>
+        <v>8.1464</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3869</v>
-      </c>
+        <v>-5.8189</v>
+      </c>
+      <c r="Y16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0771</v>
+        <v>8.691800000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8962</v>
+        <v>7.172</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1809</v>
+        <v>1.5198</v>
       </c>
       <c r="G17" t="n">
-        <v>3.0711</v>
+        <v>8.127000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1842</v>
+        <v>5.3753</v>
       </c>
       <c r="I17" t="n">
-        <v>2.8869</v>
+        <v>2.7517</v>
       </c>
       <c r="J17" t="n">
-        <v>3.3057</v>
+        <v>7.6776</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1483</v>
+        <v>5.0601</v>
       </c>
       <c r="L17" t="n">
-        <v>3.1573</v>
+        <v>2.6174</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.2346</v>
+        <v>0.4494</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0359</v>
+        <v>0.3152</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2704</v>
+        <v>0.1342</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6266</v>
+        <v>0.9946</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0834</v>
+        <v>0.6357</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.71</v>
+        <v>0.3589</v>
       </c>
       <c r="V17" t="n">
-        <v>1.8279</v>
+        <v>-1.9925</v>
       </c>
       <c r="W17" t="n">
-        <v>2.4373</v>
+        <v>-0.1646</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6093</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>G. DI BONAVENTURA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.9215</v>
+        <v>5.8411</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5623</v>
+        <v>3.23</v>
       </c>
       <c r="F18" t="n">
-        <v>2.3592</v>
+        <v>2.6111</v>
       </c>
       <c r="G18" t="n">
-        <v>3.7851</v>
+        <v>2.8737</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7583</v>
+        <v>1.6455</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0268</v>
+        <v>1.2282</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0011</v>
+        <v>2.7637</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3781</v>
+        <v>1.5349</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.377</v>
+        <v>1.2288</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7841</v>
+        <v>0.11</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3802</v>
+        <v>0.1105</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4039</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7348</v>
+        <v>2.5395</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5736</v>
+        <v>-0.2009</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5147</v>
+        <v>0.2244</v>
       </c>
       <c r="U18" t="n">
-        <v>0.059</v>
+        <v>-0.4252</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.2186</v>
+        <v>1.6056</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6820000000000001</v>
+        <v>4.0771</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4794</v>
+        <v>2.8962</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2026</v>
+        <v>1.1809</v>
       </c>
       <c r="G19" t="n">
-        <v>3.4313</v>
+        <v>3.0711</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4216</v>
+        <v>0.1842</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0097</v>
+        <v>2.8869</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5723</v>
+        <v>3.3057</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6971000000000001</v>
+        <v>0.1483</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8752</v>
+        <v>3.1573</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8589</v>
+        <v>-0.2346</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7245</v>
+        <v>0.0359</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1344</v>
+        <v>-0.2704</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6404</v>
+        <v>-0.6266</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1395</v>
+        <v>0.0834</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5009</v>
+        <v>-0.71</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.7182</v>
+        <v>1.8279</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.4373</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.7182</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.618</v>
+        <v>3.9215</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.257</v>
+        <v>1.5623</v>
       </c>
       <c r="F20" t="n">
-        <v>1.875</v>
+        <v>2.3592</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6614</v>
+        <v>3.7851</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0256</v>
+        <v>3.7583</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3642</v>
+        <v>0.0268</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0622</v>
+        <v>3.0011</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6958</v>
+        <v>3.3781</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-0.377</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5992</v>
+        <v>0.7841</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3298</v>
+        <v>0.3802</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2694</v>
+        <v>0.4039</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>2.7348</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3522</v>
+        <v>0.5736</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3425</v>
+        <v>0.5147</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0097</v>
+        <v>0.059</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1025</v>
+        <v>1.214</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1424</v>
+        <v>1.214</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0398</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7374000000000001</v>
+        <v>1.214</v>
       </c>
       <c r="H21" t="n">
-        <v>1.075</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3375</v>
+        <v>1.214</v>
       </c>
       <c r="J21" t="n">
-        <v>1.0222</v>
+        <v>1.214</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8199</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2023</v>
+        <v>1.214</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2848</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2551</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4959</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1562</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3397</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7731</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3622</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7973</v>
+        <v>0.4794</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1595</v>
+        <v>0.2026</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.2212</v>
+        <v>3.4313</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7224</v>
+        <v>1.4216</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4988</v>
+        <v>2.0097</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5927</v>
+        <v>2.5723</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0409</v>
+        <v>0.6971000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6336000000000001</v>
+        <v>1.8752</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.8589</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7634</v>
+        <v>0.7245</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1348</v>
+        <v>0.1344</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8907</v>
+        <v>-0.6404</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3831</v>
+        <v>-0.1395</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5077</v>
+        <v>-0.5009</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5545</v>
+        <v>-1.7182</v>
       </c>
       <c r="W22" t="n">
-        <v>1.7731</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-1.7182</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>P. MARTÍNEZ FERIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9989</v>
+        <v>0.614</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1637</v>
+        <v>0.614</v>
       </c>
       <c r="F23" t="n">
-        <v>1.1648</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.0392</v>
+        <v>0.614</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.4301</v>
+        <v>0.614</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3908</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2243</v>
+        <v>0.614</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3457</v>
+        <v>0.614</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.185</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0844</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2694</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1197</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0689</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1886</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0.3869</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,58 +2392,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.4215</v>
+        <v>0.0041</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9686</v>
+        <v>-1.871</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4528</v>
+        <v>1.875</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3334</v>
+        <v>0.0474</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1985</v>
+        <v>0.4116</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1348</v>
+        <v>-0.3642</v>
       </c>
       <c r="J24" t="n">
-        <v>0.3479</v>
+        <v>-0.5518</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3479</v>
+        <v>0.0819</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.0146</v>
+        <v>0.5992</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1494</v>
+        <v>0.3298</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1348</v>
+        <v>0.2694</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7195</v>
+        <v>-0.3522</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3631</v>
+        <v>-0.3425</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3564</v>
+        <v>-0.0097</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2772</v>
@@ -2342,12 +2453,17 @@
       </c>
       <c r="X24" t="n">
         <v>-0.2772</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,401 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.1604</v>
+        <v>-1.1025</v>
       </c>
       <c r="E25" t="n">
-        <v>9.8195</v>
+        <v>-1.1424</v>
       </c>
       <c r="F25" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.7374000000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.075</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.3375</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.0222</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.8199</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.2023</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.2848</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.2551</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.5399</v>
+      </c>
+      <c r="P25" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4959</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.1562</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-1.1638</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.6093</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-1.7731</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>M. FENES HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.3622</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7973</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-2.1595</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.2212</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.7224</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-0.4988</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-0.5927</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-0.6284999999999999</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-0.7634</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.8907</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.3831</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.5077</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.7731</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>U. FERNANDEZ RUIZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-1.9989</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.1637</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.1648</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-1.0392</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.4301</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.2243</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.3457</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.1214</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-0.0844</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.1197</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.0689</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.1886</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.0549</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>B. ROS FERNANDEZ</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-2.4215</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.9686</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.4528</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1985</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.1494</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.1953</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.7195</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.3631</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-0.3564</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484324_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>18.1605</v>
+      </c>
+      <c r="E29" t="n">
+        <v>9.819499999999996</v>
+      </c>
+      <c r="F29" t="n">
         <v>8.3409</v>
       </c>
-      <c r="G25" t="n">
+      <c r="G29" t="n">
         <v>21.974</v>
       </c>
-      <c r="H25" t="n">
+      <c r="H29" t="n">
         <v>12.5315</v>
       </c>
-      <c r="I25" t="n">
-        <v>9.442300000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>20.1496</v>
-      </c>
-      <c r="K25" t="n">
-        <v>11.3773</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="I29" t="n">
+        <v>9.442400000000001</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20.1497</v>
+      </c>
+      <c r="K29" t="n">
+        <v>11.3774</v>
+      </c>
+      <c r="L29" t="n">
         <v>8.7722</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M29" t="n">
         <v>1.8241</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N29" t="n">
         <v>1.154</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O29" t="n">
         <v>0.6699999999999999</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P29" t="n">
         <v>-0.0001999999999997559</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q29" t="n">
         <v>-16.6039</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>16.6041</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>-1.4859</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>0.4551000000000001</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>-1.9409</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>-2.3274</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>5.8188</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X29" t="n">
         <v>-8.1463</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
